--- a/data/tags/אלבומים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דודו טסה – אי</v>
+        <v>אייל גולן - GOLD 2025</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%95%d7%93%d7%95-%d7%98%d7%a1%d7%94-%d7%90%d7%99/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24446&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מי מוציא היום אלבום של 18 שירים? התשובה: דודו טסה. הוא עזב את הכאוס המקומי, יצא לאי ביוון עם עלמה זוהר ויונתן דסקל, והנה התוצאה. שווה היה להתנתק. הנה מה שהאי הוליד. שווה מאוד להקשיב. האלבום נפתח ב"עמנואל" – לא</v>
+        <v>00:20</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דודו טסה – אי</v>
+        <v>אייל גולן - GOLD 2025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>עברי לידר - אין לך מילה</v>
+        <v>דודו טסה - אי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24444&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24449&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>19:24</v>
+        <v>19:23</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>עברי לידר - אין לך מילה</v>
+        <v>דודו טסה - אי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יובל בנאי - אודיסאוס של הרכבת התחתית</v>
+        <v>אתי אנקרי - אורייתא</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-15</v>
       </c>
       <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24445&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24447&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-15</v>
+        <v>2026-02-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,88 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יובל בנאי - אודיסאוס של הרכבת התחתית</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>מתי כספי ז''ל הזמר, מענקי המוזיקה שלנו הלך הלילה לעולמו - יהי זכרו ברוך</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-14</v>
-      </c>
-      <c r="C5" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24443&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>07:49</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>מתי כספי ז''ל הזמר, מענקי המוזיקה שלנו הלך הלילה לעולמו - יהי זכרו ברוך</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>הפטריקים - הפרויקט של דודי לוי ואבטיפוס - להיטי הזהב</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-13</v>
-      </c>
-      <c r="C6" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24448&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v>00:30</v>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>הפטריקים - הפרויקט של דודי לוי ואבטיפוס - להיטי הזהב</v>
+        <v>אתי אנקרי - אורייתא</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-02-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן - GOLD 2025</v>
+        <v>אייל גולן - בדרך ל-30 EP</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24446&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24450&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>00:20</v>
+        <v>04:00</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,88 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן - GOLD 2025</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>דודו טסה - אי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24449&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>19:23</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>דודו טסה - אי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>אתי אנקרי - אורייתא</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24447&amp;forum=music&amp;viewmode=all</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>19:23</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>אלבומים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>אתי אנקרי - אורייתא</v>
+        <v>אייל גולן - בדרך ל-30 EP</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/אלבומים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-02-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אייל גולן - בדרך ל-30 EP</v>
+        <v>אילן וירצברג - אילן בן עשרים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-17</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24450&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24451&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>04:00</v>
+        <v>22:01</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אייל גולן - בדרך ל-30 EP</v>
+        <v>אילן וירצברג - אילן בן עשרים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-02-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אילן וירצברג - אילן בן עשרים</v>
+        <v>עומר אדם - חלק מהנצח</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-17</v>
+        <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24451&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24453&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-18</v>
+        <v>2026-02-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22:01</v>
+        <v>20:42</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אילן וירצברג - אילן בן עשרים</v>
+        <v>עומר אדם - חלק מהנצח</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-02-week03/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עומר אדם - חלק מהנצח</v>
+        <v>שלומי שבן - חי בגימל בהיכל התרבות</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-19</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24453&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24454&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-19</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20:42</v>
+        <v>20:44</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עומר אדם - חלק מהנצח</v>
+        <v>שלומי שבן - חי בגימל בהיכל התרבות</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/2026-02-week03/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-02-week03/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי שבן - חי בגימל בהיכל התרבות</v>
+        <v>שלומי שבן חי בגימל בהיכל התרבות</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24454&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%9f-%d7%97%d7%99-%d7%91%d7%92%d7%99%d7%9e%d7%9c-%d7%91%d7%94%d7%99%d7%9b%d7%9c-%d7%94%d7%aa%d7%a8%d7%91%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-19</v>
+        <v>2026-02-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20:44</v>
+        <v>יש סיבה לחזור להיכל התרבות הריק מאדם למפגשי הקורונה של שלומי שבן.  האלבום "חי בגימל בהיכל התרבות" של שלומי שבן שנולד בתקופת הסגרים בקורונה, הוא לא עוד פרויקט קאברים – הוא תיעוד של מצב תרבותי חריג: אין קהל, אין להקה,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי שבן - חי בגימל בהיכל התרבות</v>
+        <v>שלומי שבן חי בגימל בהיכל התרבות</v>
       </c>
     </row>
   </sheetData>
